--- a/tests/fixtures/hyou-no-soto-sample.xlsx
+++ b/tests/fixtures/hyou-no-soto-sample.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zeroa\exally-prod\tests\fixtures\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zeroa\AppData\Local\Temp\exally-mihon\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{69788781-EA53-40DA-8AE1-7F35DEC64DF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FA69F8A0-FB6B-49EE-96C6-2924B547776A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21323" windowHeight="11107" xr2:uid="{2338C5FB-A79B-4BF1-8E50-083C60C8D858}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="11625" xr2:uid="{5A29FF74-2F6E-48A8-BB44-AD70189BC82E}"/>
   </bookViews>
   <sheets>
     <sheet name="計算" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
     <t>数</t>
   </si>
   <si>
-    <t>正岡ｈ</t>
+    <t>標本七ｈ</t>
   </si>
 </sst>
 </file>
@@ -119,25 +119,25 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{489C0556-3A62-4B45-A967-80228363CB74}" name="R8.8" displayName="R8.8" ref="A1:C5" totalsRowShown="0">
-  <autoFilter ref="A1:C5" xr:uid="{489C0556-3A62-4B45-A967-80228363CB74}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0E04BD6C-F569-465E-9621-78F96F20CC84}" name="R8.8" displayName="R8.8" ref="A1:C5" totalsRowShown="0">
+  <autoFilter ref="A1:C5" xr:uid="{0E04BD6C-F569-465E-9621-78F96F20CC84}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{20015C4D-EED7-4314-BE26-72207B1C10B0}" name="日付"/>
-    <tableColumn id="2" xr3:uid="{CEF55FA2-A7E2-4DD6-881E-6CDE678D0893}" name="数"/>
-    <tableColumn id="3" xr3:uid="{9425075D-F0A4-455F-9321-3FDDCB206636}" name="正岡ｈ"/>
+    <tableColumn id="1" xr3:uid="{97629836-D713-4504-A4F1-8CA30B900890}" name="日付"/>
+    <tableColumn id="2" xr3:uid="{51CB6F19-253E-421F-8CCE-0FBC26D1260E}" name="数"/>
+    <tableColumn id="3" xr3:uid="{DB8A7FF1-2E82-4BA2-9906-2C890ED22E2B}" name="標本七ｈ"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{9E6D540B-0914-481C-9748-F5A5C7EBBD3C}" name="R8.9" displayName="R8.9" ref="A8:C12" totalsRowShown="0">
-  <autoFilter ref="A8:C12" xr:uid="{9E6D540B-0914-481C-9748-F5A5C7EBBD3C}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{CE18023A-2E20-4909-AE83-29C142F7AB64}" name="R8.9" displayName="R8.9" ref="A8:C12" totalsRowShown="0">
+  <autoFilter ref="A8:C12" xr:uid="{CE18023A-2E20-4909-AE83-29C142F7AB64}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{2209833F-2166-4C25-B829-E0A0340DD40A}" name="日付"/>
-    <tableColumn id="2" xr3:uid="{CD091AE5-C374-4D32-9AEE-99BE0C62CE00}" name="数"/>
-    <tableColumn id="3" xr3:uid="{6B35148A-4F6F-4F5D-A122-43629CD143B6}" name="正岡ｈ" dataDxfId="0">
-      <calculatedColumnFormula>IFERROR(MAX(R8.9[[#This Row],[数]]*2, 1000*R8.8[[#This Row],[正岡ｈ]]), 0)</calculatedColumnFormula>
+    <tableColumn id="1" xr3:uid="{05BD8D8F-BA03-4FAF-9D00-B6F32D4FB798}" name="日付"/>
+    <tableColumn id="2" xr3:uid="{F6A58F72-D12A-4214-882D-563766D9CDDD}" name="数"/>
+    <tableColumn id="3" xr3:uid="{75757117-F509-44BD-B47F-DC7F0E36C2A4}" name="標本七ｈ" dataDxfId="0">
+      <calculatedColumnFormula>IFERROR(MAX(R8.9[[#This Row],[数]]*2, 1000*R8.8[[#This Row],[標本七ｈ]]), 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -460,9 +460,12 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{345B77B7-0E5D-40E2-9C5B-491CC5DD79C8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0575BC5A-52D4-4E7E-9551-E4D707CA1E9C}">
   <dimension ref="A1:C12"/>
   <sheetFormatPr defaultRowHeight="17.649999999999999" x14ac:dyDescent="0.7"/>
+  <cols>
+    <col min="3" max="3" width="9.6875" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A1" t="s">
@@ -538,7 +541,7 @@
         <v>18</v>
       </c>
       <c r="C9">
-        <f>IFERROR(MAX(R8.9[[#This Row],[数]]*2, 1000*R8.8[[#This Row],[正岡ｈ]]), 0)</f>
+        <f>IFERROR(MAX(R8.9[[#This Row],[数]]*2, 1000*R8.8[[#This Row],[標本七ｈ]]), 0)</f>
         <v>0</v>
       </c>
     </row>
@@ -550,7 +553,7 @@
         <v>20</v>
       </c>
       <c r="C10">
-        <f>IFERROR(MAX(R8.9[[#This Row],[数]]*2, 1000*R8.8[[#This Row],[正岡ｈ]]), 0)</f>
+        <f>IFERROR(MAX(R8.9[[#This Row],[数]]*2, 1000*R8.8[[#This Row],[標本七ｈ]]), 0)</f>
         <v>0</v>
       </c>
     </row>
@@ -562,7 +565,7 @@
         <v>22</v>
       </c>
       <c r="C11">
-        <f>IFERROR(MAX(R8.9[[#This Row],[数]]*2, 1000*R8.8[[#This Row],[正岡ｈ]]), 0)</f>
+        <f>IFERROR(MAX(R8.9[[#This Row],[数]]*2, 1000*R8.8[[#This Row],[標本七ｈ]]), 0)</f>
         <v>0</v>
       </c>
     </row>
@@ -574,7 +577,7 @@
         <v>24</v>
       </c>
       <c r="C12">
-        <f>IFERROR(MAX(R8.9[[#This Row],[数]]*2, 1000*R8.8[[#This Row],[正岡ｈ]]), 0)</f>
+        <f>IFERROR(MAX(R8.9[[#This Row],[数]]*2, 1000*R8.8[[#This Row],[標本七ｈ]]), 0)</f>
         <v>0</v>
       </c>
     </row>

--- a/tests/fixtures/hyou-no-soto-sample.xlsx
+++ b/tests/fixtures/hyou-no-soto-sample.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zeroa\AppData\Local\Temp\exally-mihon\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url=""/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{FA69F8A0-FB6B-49EE-96C6-2924B547776A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
